--- a/3.Understand/EE6407-热门考点分析.xlsx
+++ b/3.Understand/EE6407-热门考点分析.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="143">
   <si>
     <t>目录</t>
   </si>
@@ -458,84 +456,6 @@
   </si>
   <si>
     <t>11.6 兰德指数</t>
-  </si>
-  <si>
-    <t>8.CK方程</t>
-  </si>
-  <si>
-    <t>9.柯尔莫哥洛夫微分方程</t>
-  </si>
-  <si>
-    <t>10.生灭过程</t>
-  </si>
-  <si>
-    <t>排队模型</t>
-  </si>
-  <si>
-    <t>1.排队</t>
-  </si>
-  <si>
-    <t>2.利特尔定律</t>
-  </si>
-  <si>
-    <t>3.M/M/1排队模型</t>
-  </si>
-  <si>
-    <t>4.M/M/1/N 排队模型</t>
-  </si>
-  <si>
-    <t>5.M/M/m 排队模型</t>
-  </si>
-  <si>
-    <t>6.批量到达队列(Mb/M/1)</t>
-  </si>
-  <si>
-    <t>决策分析</t>
-  </si>
-  <si>
-    <t>1.确定性下的决策</t>
-  </si>
-  <si>
-    <t>1.1层次分析法</t>
-  </si>
-  <si>
-    <t>2.风险下的决策</t>
-  </si>
-  <si>
-    <t>2.1期望收益</t>
-  </si>
-  <si>
-    <t>2.2决策树分析</t>
-  </si>
-  <si>
-    <t>2.3效用理论</t>
-  </si>
-  <si>
-    <t>2.4冯·诺伊曼-摩根斯坦方法</t>
-  </si>
-  <si>
-    <t>2.5将风险纳入决策树分析</t>
-  </si>
-  <si>
-    <t>2.6信息的价值</t>
-  </si>
-  <si>
-    <t>3.不确定性下的决策</t>
-  </si>
-  <si>
-    <t>3.1. 悲观标准（Maximin标准）</t>
-  </si>
-  <si>
-    <t>3.2. 乐观准则（Maximax）</t>
-  </si>
-  <si>
-    <t>3.3. 赫维奇准则（Copt）</t>
-  </si>
-  <si>
-    <t>3.4. 后悔标准（萨维奇标准）</t>
-  </si>
-  <si>
-    <t>3.5. 拉普拉斯的标准</t>
   </si>
 </sst>
 </file>
@@ -557,12 +477,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -571,6 +485,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -719,7 +639,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -728,6 +648,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -740,19 +666,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.35"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1108,7 +1022,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1132,16 +1046,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1150,156 +1064,135 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1616,674 +1509,676 @@
   <dimension ref="A1:G94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="32.1818181818182" style="11" customWidth="1"/>
-    <col min="2" max="7" width="27.0909090909091" style="11" customWidth="1"/>
-    <col min="8" max="8" width="14.5454545454545" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="32.1818181818182" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.0909090909091" style="5" customWidth="1"/>
+    <col min="3" max="3" width="35.2727272727273" style="5" customWidth="1"/>
+    <col min="4" max="7" width="27.0909090909091" style="5" customWidth="1"/>
+    <col min="8" max="8" width="14.5454545454545" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:7">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="1" spans="1:1">
-      <c r="A2" s="12" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:1">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="9" customFormat="1" spans="1:1">
-      <c r="A3" s="13" t="s">
+    <row r="3" s="3" customFormat="1" spans="1:1">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="14" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" s="9" customFormat="1" spans="1:1">
-      <c r="A8" s="13" t="s">
+    <row r="8" s="3" customFormat="1" spans="1:1">
+      <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" s="9" customFormat="1" spans="1:1">
-      <c r="A9" s="13" t="s">
+    <row r="9" s="3" customFormat="1" spans="1:1">
+      <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" s="10" customFormat="1" spans="1:7">
-      <c r="A10" s="15" t="s">
+    <row r="10" s="4" customFormat="1" spans="1:7">
+      <c r="A10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="E10" s="15" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="E10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" s="10" customFormat="1" spans="1:6">
-      <c r="A11" s="17" t="s">
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="1:6">
+      <c r="A11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" s="10" customFormat="1" spans="1:1">
-      <c r="A12" s="10" t="s">
+    <row r="12" s="4" customFormat="1" spans="1:1">
+      <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" s="10" customFormat="1" spans="1:1">
-      <c r="A13" s="10" t="s">
+    <row r="13" s="4" customFormat="1" spans="1:1">
+      <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" s="10" customFormat="1" spans="1:1">
-      <c r="A14" s="10" t="s">
+    <row r="14" s="4" customFormat="1" spans="1:1">
+      <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" s="10" customFormat="1" spans="1:5">
-      <c r="A15" s="14" t="s">
+    <row r="15" s="4" customFormat="1" spans="1:5">
+      <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" s="10" customFormat="1" spans="1:1">
-      <c r="A16" s="10" t="s">
+    <row r="16" s="4" customFormat="1" spans="1:1">
+      <c r="A16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" s="9" customFormat="1" spans="1:1">
-      <c r="A17" s="13" t="s">
+    <row r="17" s="3" customFormat="1" spans="1:1">
+      <c r="A17" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" s="9" customFormat="1" spans="1:1">
-      <c r="A25" s="13" t="s">
+    <row r="25" s="3" customFormat="1" spans="1:1">
+      <c r="A25" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" s="8" customFormat="1" spans="1:1">
-      <c r="A26" s="12" t="s">
+    <row r="26" s="2" customFormat="1" spans="1:1">
+      <c r="A26" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" s="9" customFormat="1" spans="1:1">
-      <c r="A27" s="13" t="s">
+    <row r="27" s="3" customFormat="1" spans="1:1">
+      <c r="A27" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" s="9" customFormat="1" spans="1:1">
-      <c r="A28" s="13" t="s">
+    <row r="28" s="3" customFormat="1" spans="1:1">
+      <c r="A28" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" s="9" customFormat="1" spans="1:1">
-      <c r="A38" s="13" t="s">
+    <row r="38" s="3" customFormat="1" spans="1:1">
+      <c r="A38" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="48" s="10" customFormat="1" spans="1:1">
-      <c r="A48" s="19" t="s">
+    <row r="48" s="4" customFormat="1" spans="1:1">
+      <c r="A48" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" s="10" customFormat="1" spans="1:4">
-      <c r="A49" s="18" t="s">
+    <row r="49" s="4" customFormat="1" spans="1:4">
+      <c r="A49" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="50" s="9" customFormat="1" spans="1:1">
-      <c r="A50" s="13" t="s">
+    <row r="50" s="3" customFormat="1" spans="1:1">
+      <c r="A50" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="5" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E56" s="18" t="s">
+      <c r="E56" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F56" s="18" t="s">
+      <c r="F56" s="11" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="8" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="65" s="9" customFormat="1" spans="1:1">
-      <c r="A65" s="13" t="s">
+    <row r="65" s="3" customFormat="1" spans="1:1">
+      <c r="A65" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="8" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="11" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="70" s="9" customFormat="1" spans="1:1">
-      <c r="A70" s="13" t="s">
+    <row r="70" s="3" customFormat="1" spans="1:1">
+      <c r="A70" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="71" s="9" customFormat="1" spans="1:1">
-      <c r="A71" s="13" t="s">
+    <row r="71" s="3" customFormat="1" spans="1:1">
+      <c r="A71" s="7" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="18" t="s">
+      <c r="A72" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="18" t="s">
+      <c r="E72" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F72" s="18" t="s">
+      <c r="F72" s="11" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="18" t="s">
+      <c r="A73" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F73" s="18" t="s">
+      <c r="F73" s="11" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="74" s="9" customFormat="1" spans="1:1">
-      <c r="A74" s="13" t="s">
+    <row r="74" s="3" customFormat="1" spans="1:1">
+      <c r="A74" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="75" s="9" customFormat="1" spans="1:1">
-      <c r="A75" s="13" t="s">
+    <row r="75" s="3" customFormat="1" spans="1:1">
+      <c r="A75" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="8" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="5" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E79" s="15" t="s">
+      <c r="E79" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F79" s="15" t="s">
+      <c r="F79" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="80" s="9" customFormat="1" spans="1:1">
-      <c r="A80" s="13" t="s">
+    <row r="80" s="3" customFormat="1" spans="1:1">
+      <c r="A80" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="18" t="s">
+      <c r="A83" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C83" s="18" t="s">
+      <c r="C83" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="F83" s="18" t="s">
+      <c r="F83" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="18" t="s">
+      <c r="A84" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D84" s="18" t="s">
+      <c r="D84" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G84" s="18" t="s">
+      <c r="G84" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E85" s="15" t="s">
+      <c r="E85" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="87" s="10" customFormat="1" spans="1:6">
-      <c r="A87" s="20" t="s">
+    <row r="87" s="4" customFormat="1" spans="1:6">
+      <c r="A87" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="E87" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F87" s="15" t="s">
+      <c r="F87" s="9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="88" s="9" customFormat="1" spans="1:1">
-      <c r="A88" s="13" t="s">
+    <row r="88" s="3" customFormat="1" spans="1:1">
+      <c r="A88" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="89" s="10" customFormat="1" spans="1:1">
-      <c r="A89" s="19" t="s">
+    <row r="89" s="4" customFormat="1" spans="1:1">
+      <c r="A89" s="12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="90" s="10" customFormat="1" spans="1:4">
-      <c r="A90" s="21" t="s">
+    <row r="90" s="4" customFormat="1" spans="1:4">
+      <c r="A90" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D90" s="18" t="s">
+      <c r="D90" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="91" s="10" customFormat="1" spans="1:4">
-      <c r="A91" s="22" t="s">
+    <row r="91" s="4" customFormat="1" spans="1:4">
+      <c r="A91" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B91" s="10"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="14" t="s">
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="92" s="10" customFormat="1" spans="1:4">
-      <c r="A92" s="22" t="s">
+    <row r="92" s="4" customFormat="1" spans="1:4">
+      <c r="A92" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="14" t="s">
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="94" s="10" customFormat="1" spans="1:4">
-      <c r="A94" s="22" t="s">
+    <row r="94" s="4" customFormat="1" spans="1:4">
+      <c r="A94" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="14" t="s">
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="8" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2292,159 +2187,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A1" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A2" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A3" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A4" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A5" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A6" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A7" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A8" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A9" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A10" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A11" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A12" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A13" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A14" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A15" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A16" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A17" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A18" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A19" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A20" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A21" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A22" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A23" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A24" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A25" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="15.5" spans="1:1">
-      <c r="A26" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>